--- a/九龙-启德-天玺．海第2A期/天玺．海第2A期_销控明细表.xlsx
+++ b/九龙-启德-天玺．海第2A期/天玺．海第2A期_销控明细表.xlsx
@@ -2536,7 +2536,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -4112,7 +4112,7 @@
           <t>A | 1150呎 (4+房)
 $5128万
 $44,591/呎
-(26年-08月-20日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">

--- a/九龙-启德-天玺．海第2A期/天玺．海第2A期_销控明细表.xlsx
+++ b/九龙-启德-天玺．海第2A期/天玺．海第2A期_销控明细表.xlsx
@@ -121,13 +121,13 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
+      <color rgb="00660000"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -272,10 +272,10 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1127,12 +1127,12 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2820,12 +2820,12 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -3875,12 +3875,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 1124呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr"/>
@@ -3899,7 +3899,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>B | 1124呎 (4+房)
 $5058万
@@ -3915,7 +3915,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>A | 1150呎 (4+房)
 $4164万
@@ -3923,7 +3923,7 @@
 (25年-04月-14日)</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>B | 1124呎 (4+房)
 $3960万
@@ -3939,7 +3939,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>A | 1150呎 (4+房)
 $4298万
@@ -3947,7 +3947,7 @@
 (25年-07月-18日)</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>B | 1124呎 (4+房)
 $4258万
@@ -3963,7 +3963,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>A | 1150呎 (4+房)
 $4095万
@@ -3971,7 +3971,7 @@
 (25年-04月-15日)</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>B | 1124呎 (4+房)
 $4520万
@@ -4019,7 +4019,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>B | 1124呎 (4+房)
 $4252万
@@ -4035,7 +4035,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>A | 1150呎 (4+房)
 $4000万
@@ -4043,7 +4043,7 @@
 (25年-05月-16日)</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>B | 1124呎 (4+房)
 $4228万
@@ -4059,15 +4059,15 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 1150呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>B | 1124呎 (4+房)
 $4019万
@@ -4083,7 +4083,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>A | 1150呎 (4+房)
 $4889万
@@ -4091,7 +4091,7 @@
 (26年-06月-26日)</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>B | 1124呎 (4+房)
 $4407万
@@ -4107,7 +4107,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>A | 1150呎 (4+房)
 $5128万
@@ -4115,7 +4115,7 @@
 (26年-09月-15日)</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>B | 1124呎 (4+房)
 $4113万
@@ -4131,7 +4131,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>A | 1150呎 (4+房)
 $4866万
@@ -4139,7 +4139,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>B | 1124呎 (4+房)
 $4251万
@@ -4155,15 +4155,15 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B20" s="21" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 1150呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>B | 1124呎 (4+房)
 $4447万
@@ -4179,7 +4179,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>A | 1150呎 (4+房)
 招标单位
@@ -4187,7 +4187,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>B | 1124呎 (4+房)
 招标单位
